--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="18187" windowHeight="7560"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="add sku field separte from barc" sheetId="1" r:id="rId4"/>
+    <sheet name="add sku field separte from barc" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>Product Line</t>
   </si>
@@ -22,9 +25,6 @@
     <t>PV</t>
   </si>
   <si>
-    <t>Buying (KSH)</t>
-  </si>
-  <si>
     <t>Selling (KSH)</t>
   </si>
   <si>
@@ -40,33 +40,60 @@
     <t>4 in 1 Reishi Coffee</t>
   </si>
   <si>
+    <t>893663002913</t>
+  </si>
+  <si>
     <t>4 in 1 Ginseng Coffee</t>
   </si>
   <si>
+    <t>893663002920</t>
+  </si>
+  <si>
     <t>4 in 1 Cordyceps Coffee</t>
   </si>
   <si>
+    <t>893663002937</t>
+  </si>
+  <si>
     <t>Pure &amp; Broken Ganoderma Spores (30's)</t>
   </si>
   <si>
+    <t>893663002128</t>
+  </si>
+  <si>
     <t>Pure &amp; Broken Ganoderma Spores (60's)</t>
   </si>
   <si>
+    <t>893663002739</t>
+  </si>
+  <si>
     <t>Pure &amp; Broken Ganoderma Oil (60's)</t>
   </si>
   <si>
+    <t>4897104470800</t>
+  </si>
+  <si>
     <t>Refined Yunzhi Capsules</t>
   </si>
   <si>
+    <t>893663002135</t>
+  </si>
+  <si>
     <t>Quad Reishi Capsules</t>
   </si>
   <si>
+    <t>893663002616</t>
+  </si>
+  <si>
     <t>Premium Selected</t>
   </si>
   <si>
     <t>YOUTH EVER</t>
   </si>
   <si>
+    <t>893663002111</t>
+  </si>
+  <si>
     <t>NMN coffee</t>
   </si>
   <si>
@@ -76,9 +103,15 @@
     <t>NMN-Sharp Mind</t>
   </si>
   <si>
+    <t>853913003848</t>
+  </si>
+  <si>
     <t>NMN DUO release</t>
   </si>
   <si>
+    <t>853913003879</t>
+  </si>
+  <si>
     <t>Bone &amp; Joint Care</t>
   </si>
   <si>
@@ -88,27 +121,48 @@
     <t>ArthroXtra Tablets</t>
   </si>
   <si>
+    <t>893663002043</t>
+  </si>
+  <si>
     <t>Zaminocal Plus</t>
   </si>
   <si>
+    <t>4897104471333</t>
+  </si>
+  <si>
     <t>GluzoJoint-Ultra Pro Tablets</t>
   </si>
   <si>
+    <t>4897104471111</t>
+  </si>
+  <si>
     <t>Cardiovascular Health</t>
   </si>
   <si>
     <t>MicrO2 Cycle Tablets</t>
   </si>
   <si>
+    <t>893663002234</t>
+  </si>
+  <si>
     <t>CereBrain Tablets</t>
   </si>
   <si>
+    <t>853913003749</t>
+  </si>
+  <si>
     <t>Relivin Tea</t>
   </si>
   <si>
+    <t>893663002647</t>
+  </si>
+  <si>
     <t>GymEffect Capsule</t>
   </si>
   <si>
+    <t>893663002609</t>
+  </si>
+  <si>
     <t>Detoxilive Capsules</t>
   </si>
   <si>
@@ -118,57 +172,108 @@
     <t>ConstiRelax Solution</t>
   </si>
   <si>
+    <t>893663002104</t>
+  </si>
+  <si>
     <t>Ntdiarr Pills (1 Dozen)</t>
   </si>
   <si>
+    <t>4895013210944</t>
+  </si>
+  <si>
     <t>Elements</t>
   </si>
   <si>
+    <t>4897104471265</t>
+  </si>
+  <si>
     <t>Novel Depile Capsules</t>
   </si>
   <si>
+    <t>893663002005</t>
+  </si>
+  <si>
     <t>Probio 3</t>
   </si>
   <si>
+    <t>4897104471067</t>
+  </si>
+  <si>
     <t>Veggie Veggie</t>
   </si>
   <si>
+    <t>4897104470718</t>
+  </si>
+  <si>
     <t>Ez-Xlim Capsule</t>
   </si>
   <si>
+    <t>853913003282</t>
+  </si>
+  <si>
     <t>Better life</t>
   </si>
   <si>
     <t>ProstatRelax Capsules</t>
   </si>
   <si>
+    <t>4897104471418</t>
+  </si>
+  <si>
     <t>X Power Man Capsules</t>
   </si>
   <si>
+    <t>853913003466</t>
+  </si>
+  <si>
     <t>Xpower Coffee for Men</t>
   </si>
   <si>
+    <t>853913003954</t>
+  </si>
+  <si>
     <t>Feminergy Capsules</t>
   </si>
   <si>
+    <t>853913003787</t>
+  </si>
+  <si>
     <t>FemiCalcium D3</t>
   </si>
   <si>
+    <t>4897104471388</t>
+  </si>
+  <si>
     <t>Femibiotics</t>
   </si>
   <si>
+    <t>4897104471210</t>
+  </si>
+  <si>
     <t>Youth Refreshing Facial Cleanser</t>
   </si>
   <si>
+    <t>853913003503</t>
+  </si>
+  <si>
     <t>Youth Essence Lotion</t>
   </si>
   <si>
+    <t>853913003572</t>
+  </si>
+  <si>
     <t>Youth Essence Toner</t>
   </si>
   <si>
+    <t>853913003565</t>
+  </si>
+  <si>
     <t>Youth Essence Facial Mask</t>
   </si>
   <si>
+    <t>853913003596</t>
+  </si>
+  <si>
     <t>Youth Essence Cream</t>
   </si>
   <si>
@@ -187,21 +292,36 @@
     <t>Calcium and Vitamin D3</t>
   </si>
   <si>
+    <t>4897104471050</t>
+  </si>
+  <si>
     <t>Sharp Vision</t>
   </si>
   <si>
+    <t>4897104471098</t>
+  </si>
+  <si>
     <t>Vitamin C Chewable</t>
   </si>
   <si>
+    <t>4897104471074</t>
+  </si>
+  <si>
     <t>Suma Living</t>
   </si>
   <si>
     <t>AnaticTM Herbal Essence Soap</t>
   </si>
   <si>
+    <t>853913003886</t>
+  </si>
+  <si>
     <t>FemiCare Feminine Cleanser</t>
   </si>
   <si>
+    <t>4895013208125</t>
+  </si>
+  <si>
     <t>Dr.Ts Toothpaste</t>
   </si>
   <si>
@@ -209,6 +329,9 @@
   </si>
   <si>
     <t>Cool Roll (1 Dozen)</t>
+  </si>
+  <si>
+    <t>4897104470114</t>
   </si>
   <si>
     <t>Registration</t>
@@ -220,61 +343,696 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -464,22 +1222,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultColWidth="12.6283185840708" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.25"/>
-    <col customWidth="1" min="2" max="2" width="39.63"/>
-    <col customWidth="1" min="7" max="7" width="23.63"/>
+    <col min="1" max="1" width="18.2477876106195" customWidth="1"/>
+    <col min="2" max="2" width="39.6283185840708" customWidth="1"/>
+    <col min="6" max="6" width="23.6283185840708" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,31 +1258,25 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>6.5</v>
       </c>
       <c r="D2" s="2">
-        <v>1755.0</v>
-      </c>
-      <c r="E2" s="3">
         <v>2281.5</v>
       </c>
-      <c r="G2" s="1">
-        <v>8.93663002913E11</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:6">
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
@@ -530,821 +1284,678 @@
         <v>6.5</v>
       </c>
       <c r="D3" s="2">
-        <v>1755.0</v>
-      </c>
-      <c r="E3" s="3">
         <v>2281.5</v>
       </c>
-      <c r="G3" s="1">
-        <v>8.9366300292E11</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:6">
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>6.5</v>
       </c>
       <c r="D4" s="2">
-        <v>1755.0</v>
-      </c>
-      <c r="E4" s="3">
         <v>2281.5</v>
       </c>
-      <c r="G4" s="1">
-        <v>8.93663002937E11</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:6">
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
-        <v>7830.0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>10179.0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>8.93663002128E11</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>10179</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:6">
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="D6" s="2">
-        <v>14850.0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>19305.0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8.93663002739E11</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>19305</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:6">
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="D7" s="2">
-        <v>17280.0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>22464.0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>4.8971044708E12</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>22464</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:6">
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2">
-        <v>3915.0</v>
-      </c>
-      <c r="E8" s="3">
         <v>5089.5</v>
       </c>
-      <c r="G8" s="1">
-        <v>8.93663002135E11</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2">
-        <v>4725.0</v>
-      </c>
-      <c r="E9" s="3">
         <v>6142.5</v>
       </c>
-      <c r="G9" s="1">
-        <v>8.93663002616E11</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2">
-        <v>13365.0</v>
-      </c>
-      <c r="E10" s="3">
         <v>17374.5</v>
       </c>
-      <c r="G10" s="1">
-        <v>8.93663002111E11</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="F10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:7">
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>12.5</v>
       </c>
       <c r="D11" s="2">
-        <v>3375.0</v>
-      </c>
-      <c r="E11" s="3">
         <v>4387.5</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="G11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:6">
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="D12" s="2">
-        <v>21600.0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>28080.0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>8.53913003848E11</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>28080</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:6">
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="D13" s="2">
-        <v>20115.0</v>
-      </c>
-      <c r="E13" s="3">
         <v>26149.5</v>
       </c>
-      <c r="G13" s="1">
-        <v>8.53913003879E11</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>23.5</v>
       </c>
       <c r="D14" s="2">
-        <v>3780.0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>4914.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>4914</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:6">
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1">
         <v>34.5</v>
       </c>
       <c r="D15" s="2">
-        <v>5400.0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>7020.0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>8.93663002043E11</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>7020</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:6">
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2">
-        <v>3105.0</v>
-      </c>
-      <c r="E16" s="3">
         <v>4036.5</v>
       </c>
-      <c r="G16" s="1">
-        <v>4.897104471333E12</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="F16" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:6">
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1">
         <v>44.8</v>
       </c>
       <c r="D17" s="2">
-        <v>7560.0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>9828.0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>4.897104471111E12</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>9828</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2">
-        <v>2970.0</v>
-      </c>
-      <c r="E18" s="3">
-        <v>3861.0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>8.93663002234E11</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>3861</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:6">
       <c r="B19" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D19" s="2">
-        <v>3375.0</v>
-      </c>
-      <c r="E19" s="3">
         <v>4387.5</v>
       </c>
-      <c r="G19" s="1">
-        <v>8.53913003749E11</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="F19" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:6">
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2">
-        <v>2430.0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>3159.0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>8.93663002647E11</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>3159</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:6">
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D21" s="2">
-        <v>2700.0</v>
-      </c>
-      <c r="E21" s="3">
-        <v>3510.0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>8.93663002609E11</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>3510</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:4">
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="E22" s="3">
         <v>2632.5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="2">
-        <v>3915.0</v>
-      </c>
-      <c r="E23" s="3">
         <v>5089.5</v>
       </c>
-      <c r="G23" s="1">
-        <v>8.93663002104E11</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="F23" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C24" s="1">
         <v>2.4</v>
       </c>
       <c r="D24" s="2">
-        <v>1620.0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2106.0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>4.895013210944E12</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>2106</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:6">
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D25" s="2">
-        <v>4050.0</v>
-      </c>
-      <c r="E25" s="3">
-        <v>5265.0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>4.897104471265E12</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>5265</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:6">
       <c r="B26" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C26" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2">
-        <v>2970.0</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3861.0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>8.93663002005E11</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>3861</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:6">
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D27" s="2">
-        <v>4050.0</v>
-      </c>
-      <c r="E27" s="3">
-        <v>5265.0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>4.897104471067E12</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>5265</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:6">
       <c r="B28" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C28" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D28" s="2">
-        <v>4050.0</v>
-      </c>
-      <c r="E28" s="3">
-        <v>5265.0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>4.897104470718E12</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>5265</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D29" s="2">
-        <v>7020.0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>9126.0</v>
-      </c>
-      <c r="G29" s="1">
-        <v>8.53913003282E11</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>9126</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C30" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2">
-        <v>3240.0</v>
-      </c>
-      <c r="E30" s="3">
-        <v>4212.0</v>
-      </c>
-      <c r="G30" s="1">
-        <v>4.897104471418E12</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>4212</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2">
-        <v>5670.0</v>
-      </c>
-      <c r="E31" s="3">
-        <v>7371.0</v>
-      </c>
-      <c r="G31" s="1">
-        <v>8.53913003466E11</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>7371</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C32" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="E32" s="3">
         <v>2632.5</v>
       </c>
-      <c r="G32" s="1">
-        <v>8.53913003954E11</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="F32" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="2:6">
       <c r="B33" s="1" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C33" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D33" s="2">
-        <v>4050.0</v>
-      </c>
-      <c r="E33" s="3">
-        <v>5265.0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>8.53913003787E11</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>5265</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="2:6">
       <c r="B34" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C34" s="1">
         <v>24.5</v>
       </c>
       <c r="D34" s="2">
-        <v>4320.0</v>
-      </c>
-      <c r="E34" s="3">
-        <v>5616.0</v>
-      </c>
-      <c r="G34" s="1">
-        <v>4.897104471388E12</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>5616</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="2:6">
       <c r="B35" s="1" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C35" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2">
-        <v>5400.0</v>
-      </c>
-      <c r="E35" s="3">
-        <v>7020.0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>4.89710447121E12</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>7020</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="2:6">
       <c r="B36" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C36" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2">
-        <v>2970.0</v>
-      </c>
-      <c r="E36" s="3">
-        <v>3861.0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>8.53913003503E11</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>3861</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="2:6">
       <c r="B37" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C37" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D37" s="2">
-        <v>3375.0</v>
-      </c>
-      <c r="E37" s="3">
         <v>4387.5</v>
       </c>
-      <c r="G37" s="1">
-        <v>8.53913003572E11</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="F37" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="2:6">
       <c r="B38" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C38" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D38" s="2">
-        <v>3645.0</v>
-      </c>
-      <c r="E38" s="3">
         <v>4738.5</v>
       </c>
-      <c r="G38" s="1">
-        <v>8.53913003565E11</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="F38" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="2:6">
       <c r="B39" s="1" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C39" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D39" s="2">
-        <v>2430.0</v>
-      </c>
-      <c r="E39" s="3">
-        <v>3159.0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>8.53913003596E11</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>3159</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="2:7">
       <c r="B40" s="1" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C40" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D40" s="2">
-        <v>4590.0</v>
-      </c>
-      <c r="E40" s="3">
-        <v>5967.0</v>
-      </c>
-      <c r="H40" s="1" t="s">
+        <v>5967</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="2:4">
+      <c r="B41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="1">
         <v>53</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="1">
-        <v>53.0</v>
-      </c>
       <c r="D41" s="2">
-        <v>9990.0</v>
-      </c>
-      <c r="E41" s="3">
-        <v>12987.0</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>12987</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:4">
       <c r="B42" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C42" s="1">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="D42" s="2">
-        <v>17010.0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>22113.0</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>22113</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C43" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D43" s="2">
-        <v>3240.0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>4212.0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>4.89710447105E12</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>4212</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C44" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D44" s="2">
-        <v>3240.0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>4212.0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>4.897104471098E12</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>4212</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:6">
       <c r="B45" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="C45" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D45" s="2">
-        <v>2700.0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3510.0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>4.897104471074E12</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>3510</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C46" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="1">
-        <v>297.0</v>
-      </c>
-      <c r="E46" s="1">
         <v>386.1</v>
       </c>
-      <c r="G46" s="1">
-        <v>8.53913003886E11</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="F46" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="2:6">
       <c r="B47" s="1" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C47" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D47" s="2">
-        <v>1485.0</v>
-      </c>
-      <c r="E47" s="3">
         <v>1930.5</v>
       </c>
-      <c r="G47" s="1">
-        <v>4.895013208125E12</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="F47" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="2:7">
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C48" s="1">
         <v>2.8</v>
       </c>
       <c r="D48" s="1">
-        <v>743.0</v>
-      </c>
-      <c r="E48" s="1">
         <v>965.25</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="G48" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="2:6">
       <c r="B49" s="1" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C49" s="1">
         <v>2.4</v>
       </c>
       <c r="D49" s="2">
-        <v>1620.0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>2106.0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>4.897104470114E12</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>2106</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D50" s="2">
-        <v>2900.0</v>
-      </c>
-      <c r="E50" s="3">
-        <v>2900.0</v>
+        <v>2900</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>Product Line</t>
   </si>
@@ -103,6 +103,9 @@
     <t>NMN coffee</t>
   </si>
   <si>
+    <t>893663002425</t>
+  </si>
+  <si>
     <t>print white</t>
   </si>
   <si>
@@ -169,7 +172,10 @@
     <t>893663002609</t>
   </si>
   <si>
-    <t>Detoxilive Capsules</t>
+    <t>Detoxilive Capsules pro</t>
+  </si>
+  <si>
+    <t>487104471401</t>
   </si>
   <si>
     <t>Digestive Health</t>
@@ -286,12 +292,6 @@
     <t>out of stock</t>
   </si>
   <si>
-    <t>SUMA GRAND 1 (Cleanser+Lotion+Toner)</t>
-  </si>
-  <si>
-    <t>SUMA GRAND 2 (Full Set)</t>
-  </si>
-  <si>
     <t>Smart Kids</t>
   </si>
   <si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Dr.Ts Toothpaste</t>
+  </si>
+  <si>
+    <t>853913003053</t>
   </si>
   <si>
     <t>print</t>
@@ -351,10 +354,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -388,46 +391,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,23 +407,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -471,22 +421,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -509,14 +444,82 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -532,187 +535,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -723,26 +726,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -761,41 +744,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,145 +776,195 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -979,6 +982,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1240,7 +1244,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="12.6283185840708" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.2477876106195" customWidth="1"/>
@@ -1283,7 +1287,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2">
         <v>6.5</v>
@@ -1303,7 +1307,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2">
         <v>6.5</v>
@@ -1323,7 +1327,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2">
         <v>6.5</v>
@@ -1343,7 +1347,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2">
         <v>52</v>
@@ -1363,7 +1367,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>99</v>
@@ -1383,7 +1387,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
         <v>102</v>
@@ -1423,7 +1427,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2">
         <v>28</v>
@@ -1446,7 +1450,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2">
         <v>79</v>
@@ -1466,7 +1470,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2">
         <v>12.5</v>
@@ -1477,13 +1481,16 @@
       <c r="F11" s="5">
         <v>3375</v>
       </c>
+      <c r="H11" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="I11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:8">
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2">
         <v>17</v>
@@ -1498,15 +1505,15 @@
         <v>21600</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:8">
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2">
         <v>112</v>
@@ -1518,15 +1525,15 @@
         <v>20115</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -1543,10 +1550,10 @@
     </row>
     <row r="15" customHeight="1" spans="2:8">
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D15" s="2">
         <v>34.5</v>
@@ -1558,15 +1565,15 @@
         <v>5400</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:8">
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2">
         <v>18</v>
@@ -1578,12 +1585,12 @@
         <v>3105</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:8">
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -1598,18 +1605,18 @@
         <v>7560</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D18" s="2">
         <v>11</v>
@@ -1621,15 +1628,15 @@
         <v>2970</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:8">
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2">
         <v>22</v>
@@ -1641,15 +1648,15 @@
         <v>3375</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:8">
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="2">
         <v>9</v>
@@ -1661,15 +1668,15 @@
         <v>2430</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:8">
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
         <v>15</v>
@@ -1681,35 +1688,38 @@
         <v>2700</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="2:6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:8">
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" s="4">
-        <v>2632.5</v>
+        <v>3510</v>
       </c>
       <c r="F22" s="5">
-        <v>2025</v>
+        <v>2700</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D23" s="2">
         <v>22</v>
@@ -1721,15 +1731,15 @@
         <v>3915</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:8">
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="D24" s="2">
         <v>2.4</v>
@@ -1741,15 +1751,15 @@
         <v>1620</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:8">
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2">
         <v>15</v>
@@ -1761,15 +1771,15 @@
         <v>4050</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:8">
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D26" s="2">
         <v>17</v>
@@ -1781,15 +1791,15 @@
         <v>2970</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:8">
       <c r="B27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2">
         <v>22</v>
@@ -1801,15 +1811,15 @@
         <v>4050</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:8">
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2">
         <v>23</v>
@@ -1821,12 +1831,12 @@
         <v>4050</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:8">
       <c r="B29" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -1841,18 +1851,18 @@
         <v>7020</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2">
         <v>18</v>
@@ -1864,15 +1874,15 @@
         <v>3240</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:8">
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2">
         <v>35</v>
@@ -1884,15 +1894,15 @@
         <v>5670</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:8">
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
         <v>8</v>
@@ -1904,15 +1914,15 @@
         <v>2025</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:8">
       <c r="B33" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D33" s="2">
         <v>25</v>
@@ -1924,15 +1934,15 @@
         <v>4050</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:8">
       <c r="B34" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2">
         <v>24.5</v>
@@ -1944,15 +1954,15 @@
         <v>4320</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:8">
       <c r="B35" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D35" s="2">
         <v>28</v>
@@ -1964,15 +1974,15 @@
         <v>5400</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:8">
       <c r="B36" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2">
         <v>15</v>
@@ -1984,15 +1994,15 @@
         <v>2970</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:8">
       <c r="B37" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2">
         <v>19</v>
@@ -2004,15 +2014,15 @@
         <v>3375</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:8">
       <c r="B38" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2">
         <v>19</v>
@@ -2024,15 +2034,15 @@
         <v>3645</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:8">
       <c r="B39" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D39" s="2">
         <v>13</v>
@@ -2044,12 +2054,12 @@
         <v>2430</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:9">
       <c r="B40" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2064,199 +2074,172 @@
         <v>4590</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="2:6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="B41" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="C41" s="2">
+        <v>13</v>
+      </c>
       <c r="D41" s="2">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E41" s="4">
-        <v>12987</v>
+        <v>4212</v>
       </c>
       <c r="F41" s="5">
-        <v>9990</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="2:6">
+        <v>3240</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:8">
       <c r="B42" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="C42" s="2">
+        <v>28</v>
+      </c>
       <c r="D42" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="E42" s="4">
-        <v>22113</v>
+        <v>4212</v>
       </c>
       <c r="F42" s="5">
-        <v>17010</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:8">
-      <c r="A43" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>3240</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:8">
       <c r="B43" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C43" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E43" s="4">
-        <v>4212</v>
+        <v>3510</v>
       </c>
       <c r="F43" s="5">
-        <v>3240</v>
+        <v>2700</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="2:8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="B44" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C44" s="2">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="D44" s="2">
-        <v>18</v>
-      </c>
-      <c r="E44" s="4">
-        <v>4212</v>
-      </c>
-      <c r="F44" s="5">
-        <v>3240</v>
+        <v>1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>386.1</v>
+      </c>
+      <c r="F44" s="3">
+        <v>297</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:8">
       <c r="B45" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D45" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E45" s="4">
-        <v>3510</v>
+        <v>1930.5</v>
       </c>
       <c r="F45" s="5">
-        <v>2700</v>
+        <v>1485</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:9">
       <c r="B46" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C46" s="2">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="D46" s="2">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="E46" s="2">
-        <v>386.1</v>
+        <v>965.25</v>
       </c>
       <c r="F46" s="3">
-        <v>297</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>101</v>
+        <v>743</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:8">
       <c r="B47" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C47" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="D47" s="2">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="E47" s="4">
-        <v>1930.5</v>
+        <v>2106</v>
       </c>
       <c r="F47" s="5">
-        <v>1485</v>
+        <v>1620</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="2:9">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:6">
+      <c r="A48" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="B48" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="2">
-        <v>142</v>
-      </c>
-      <c r="D48" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="E48" s="2">
-        <v>965.25</v>
-      </c>
-      <c r="F48" s="3">
-        <v>743</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="2:8">
-      <c r="B49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="2">
-        <v>229</v>
-      </c>
-      <c r="D49" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="E49" s="4">
-        <v>2106</v>
-      </c>
-      <c r="F49" s="5">
-        <v>1620</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:6">
-      <c r="A50" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50">
-        <v>70</v>
-      </c>
-      <c r="E50" s="4">
+        <v>110</v>
+      </c>
+      <c r="C48">
+        <v>63</v>
+      </c>
+      <c r="E48" s="4">
         <v>2900</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F48" s="5">
         <v>2900</v>
       </c>
     </row>

--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>Product Line</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>487104471401</t>
+  </si>
+  <si>
+    <t>add</t>
   </si>
   <si>
     <t>Digestive Health</t>
@@ -354,10 +357,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -383,6 +386,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -391,7 +417,97 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -407,124 +523,11 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -535,115 +538,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,67 +712,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -729,17 +732,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,8 +753,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -792,17 +789,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -818,156 +804,173 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1287,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2">
         <v>6.5</v>
@@ -1307,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2">
         <v>6.5</v>
@@ -1327,7 +1330,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2">
         <v>6.5</v>
@@ -1347,7 +1350,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2">
         <v>52</v>
@@ -1367,7 +1370,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="2">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2">
         <v>99</v>
@@ -1387,7 +1390,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2">
         <v>102</v>
@@ -1407,7 +1410,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2">
         <v>24</v>
@@ -1450,7 +1453,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2">
         <v>79</v>
@@ -1470,7 +1473,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2">
         <v>12.5</v>
@@ -1493,7 +1496,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2">
         <v>128</v>
@@ -1553,7 +1556,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="2">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D15" s="2">
         <v>34.5</v>
@@ -1573,7 +1576,7 @@
         <v>39</v>
       </c>
       <c r="C16" s="2">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2">
         <v>18</v>
@@ -1616,7 +1619,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2">
         <v>11</v>
@@ -1636,7 +1639,7 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2">
         <v>22</v>
@@ -1656,7 +1659,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2">
         <v>9</v>
@@ -1676,7 +1679,7 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D21" s="2">
         <v>15</v>
@@ -1691,12 +1694,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:8">
+    <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D22" s="2">
         <v>15</v>
@@ -1710,16 +1713,19 @@
       <c r="H22" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="I22" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D23" s="2">
         <v>22</v>
@@ -1731,15 +1737,15 @@
         <v>3915</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:8">
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D24" s="2">
         <v>2.4</v>
@@ -1751,12 +1757,12 @@
         <v>1620</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:8">
       <c r="B25" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2">
         <v>25</v>
@@ -1771,15 +1777,15 @@
         <v>4050</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:8">
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2">
         <v>17</v>
@@ -1791,15 +1797,15 @@
         <v>2970</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:8">
       <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2">
         <v>63</v>
-      </c>
-      <c r="C27" s="2">
-        <v>39</v>
       </c>
       <c r="D27" s="2">
         <v>22</v>
@@ -1811,15 +1817,15 @@
         <v>4050</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:8">
       <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D28" s="2">
         <v>23</v>
@@ -1831,12 +1837,12 @@
         <v>4050</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:8">
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -1851,18 +1857,18 @@
         <v>7020</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2">
         <v>18</v>
@@ -1874,15 +1880,15 @@
         <v>3240</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:8">
       <c r="B31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2">
         <v>35</v>
@@ -1894,15 +1900,15 @@
         <v>5670</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:8">
       <c r="B32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2">
         <v>8</v>
@@ -1914,15 +1920,15 @@
         <v>2025</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:8">
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D33" s="2">
         <v>25</v>
@@ -1934,15 +1940,15 @@
         <v>4050</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:8">
       <c r="B34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D34" s="2">
         <v>24.5</v>
@@ -1954,12 +1960,12 @@
         <v>4320</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:8">
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2">
         <v>19</v>
@@ -1974,15 +1980,15 @@
         <v>5400</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:8">
       <c r="B36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2">
         <v>15</v>
@@ -1994,12 +2000,12 @@
         <v>2970</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:8">
       <c r="B37" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -2014,15 +2020,15 @@
         <v>3375</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:8">
       <c r="B38" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D38" s="2">
         <v>19</v>
@@ -2034,15 +2040,15 @@
         <v>3645</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:8">
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2">
         <v>13</v>
@@ -2054,12 +2060,12 @@
         <v>2430</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:9">
       <c r="B40" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2074,15 +2080,15 @@
         <v>4590</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" s="2">
         <v>13</v>
@@ -2097,12 +2103,12 @@
         <v>3240</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:8">
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2">
         <v>28</v>
@@ -2117,15 +2123,15 @@
         <v>3240</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:8">
       <c r="B43" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D43" s="2">
         <v>15</v>
@@ -2137,18 +2143,18 @@
         <v>2700</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="2">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -2160,15 +2166,15 @@
         <v>297</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:8">
       <c r="B45" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D45" s="2">
         <v>6</v>
@@ -2180,15 +2186,15 @@
         <v>1485</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:9">
       <c r="B46" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" s="2">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D46" s="2">
         <v>2.8</v>
@@ -2200,18 +2206,18 @@
         <v>743</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:8">
       <c r="B47" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D47" s="2">
         <v>2.4</v>
@@ -2223,18 +2229,18 @@
         <v>1620</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:6">
       <c r="A48" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E48" s="4">
         <v>2900</v>

--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -357,9 +357,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -378,9 +378,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,9 +416,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -410,29 +431,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,18 +468,33 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -478,56 +514,20 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -538,19 +538,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,13 +652,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,90 +706,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -671,54 +719,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,24 +741,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -770,36 +752,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -821,6 +773,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -829,151 +805,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2111,7 +2111,7 @@
         <v>96</v>
       </c>
       <c r="C42" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D42" s="2">
         <v>18</v>

--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -349,7 +349,7 @@
     <t>Registration</t>
   </si>
   <si>
-    <t>Registration Fee</t>
+    <t>Registration Kit</t>
   </si>
 </sst>
 </file>
@@ -357,10 +357,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -373,6 +373,22 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -393,8 +409,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -408,8 +454,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -417,21 +486,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,16 +499,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -467,24 +514,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -492,38 +523,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -538,187 +538,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,6 +741,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -752,56 +761,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -829,151 +788,192 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1310,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2">
         <v>6.5</v>
@@ -1330,7 +1330,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2">
         <v>6.5</v>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D5" s="2">
         <v>52</v>
@@ -1370,7 +1370,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="2">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2">
         <v>99</v>
@@ -1390,7 +1390,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
         <v>102</v>
@@ -1410,7 +1410,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2">
         <v>24</v>
@@ -1430,7 +1430,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2">
         <v>28</v>
@@ -1453,7 +1453,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2">
         <v>79</v>
@@ -1473,7 +1473,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
         <v>12.5</v>
@@ -1496,7 +1496,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2">
         <v>128</v>
@@ -1556,7 +1556,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D15" s="2">
         <v>34.5</v>
@@ -1576,7 +1576,7 @@
         <v>39</v>
       </c>
       <c r="C16" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2">
         <v>18</v>
@@ -1619,7 +1619,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D18" s="2">
         <v>11</v>
@@ -1639,7 +1639,7 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D19" s="2">
         <v>22</v>
@@ -1659,7 +1659,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2">
         <v>9</v>
@@ -1679,7 +1679,7 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2">
         <v>15</v>
@@ -1725,7 +1725,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
         <v>22</v>
@@ -1745,7 +1745,7 @@
         <v>58</v>
       </c>
       <c r="C24" s="2">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D24" s="2">
         <v>2.4</v>
@@ -1765,7 +1765,7 @@
         <v>60</v>
       </c>
       <c r="C25" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>15</v>
@@ -1785,7 +1785,7 @@
         <v>62</v>
       </c>
       <c r="C26" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D26" s="2">
         <v>17</v>
@@ -1805,7 +1805,7 @@
         <v>64</v>
       </c>
       <c r="C27" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2">
         <v>22</v>
@@ -1825,7 +1825,7 @@
         <v>66</v>
       </c>
       <c r="C28" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="2">
         <v>23</v>
@@ -1868,7 +1868,7 @@
         <v>71</v>
       </c>
       <c r="C30" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2">
         <v>18</v>
@@ -1888,7 +1888,7 @@
         <v>73</v>
       </c>
       <c r="C31" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2">
         <v>35</v>
@@ -1908,7 +1908,7 @@
         <v>75</v>
       </c>
       <c r="C32" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D32" s="2">
         <v>8</v>
@@ -1928,7 +1928,7 @@
         <v>77</v>
       </c>
       <c r="C33" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2">
         <v>25</v>
@@ -1948,7 +1948,7 @@
         <v>79</v>
       </c>
       <c r="C34" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D34" s="2">
         <v>24.5</v>
@@ -1968,7 +1968,7 @@
         <v>81</v>
       </c>
       <c r="C35" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35" s="2">
         <v>28</v>
@@ -2111,7 +2111,7 @@
         <v>96</v>
       </c>
       <c r="C42" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D42" s="2">
         <v>18</v>
@@ -2131,7 +2131,7 @@
         <v>98</v>
       </c>
       <c r="C43" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2">
         <v>15</v>
@@ -2154,7 +2154,7 @@
         <v>101</v>
       </c>
       <c r="C44" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>103</v>
       </c>
       <c r="C45" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D45" s="2">
         <v>6</v>
@@ -2194,7 +2194,7 @@
         <v>105</v>
       </c>
       <c r="C46" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D46" s="2">
         <v>2.8</v>
@@ -2217,7 +2217,7 @@
         <v>108</v>
       </c>
       <c r="C47" s="2">
-        <v>253</v>
+        <v>22</v>
       </c>
       <c r="D47" s="2">
         <v>2.4</v>

--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -358,9 +358,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -378,11 +378,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -395,9 +424,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -409,18 +445,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -433,14 +492,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -449,13 +508,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -471,58 +523,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
@@ -538,157 +538,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,18 +713,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -735,7 +735,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -745,7 +756,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,8 +794,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -785,32 +811,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -832,148 +832,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1290,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2">
         <v>6.5</v>
@@ -1310,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2">
         <v>6.5</v>
@@ -1330,7 +1330,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" s="2">
         <v>6.5</v>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2">
         <v>52</v>
@@ -1370,7 +1370,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2">
         <v>99</v>
@@ -1390,7 +1390,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
         <v>102</v>
@@ -1410,7 +1410,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2">
         <v>24</v>
@@ -1430,7 +1430,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
         <v>28</v>
@@ -1453,7 +1453,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2">
         <v>79</v>
@@ -1473,7 +1473,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2">
         <v>12.5</v>
@@ -1496,7 +1496,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2">
         <v>128</v>
@@ -1516,7 +1516,7 @@
         <v>33</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
         <v>112</v>
@@ -1556,7 +1556,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D15" s="2">
         <v>34.5</v>
@@ -1576,7 +1576,7 @@
         <v>39</v>
       </c>
       <c r="C16" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2">
         <v>18</v>
@@ -1619,7 +1619,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D18" s="2">
         <v>11</v>
@@ -1639,7 +1639,7 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2">
         <v>22</v>
@@ -1659,7 +1659,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D20" s="2">
         <v>9</v>
@@ -1679,7 +1679,7 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2">
         <v>15</v>
@@ -1699,7 +1699,7 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2">
         <v>15</v>
@@ -1725,7 +1725,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D23" s="2">
         <v>22</v>
@@ -1765,7 +1765,7 @@
         <v>60</v>
       </c>
       <c r="C25" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D25" s="2">
         <v>15</v>
@@ -1805,7 +1805,7 @@
         <v>64</v>
       </c>
       <c r="C27" s="2">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D27" s="2">
         <v>22</v>
@@ -1825,7 +1825,7 @@
         <v>66</v>
       </c>
       <c r="C28" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2">
         <v>23</v>
@@ -1868,7 +1868,7 @@
         <v>71</v>
       </c>
       <c r="C30" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D30" s="2">
         <v>18</v>
@@ -1888,7 +1888,7 @@
         <v>73</v>
       </c>
       <c r="C31" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2">
         <v>35</v>
@@ -1908,7 +1908,7 @@
         <v>75</v>
       </c>
       <c r="C32" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2">
         <v>8</v>
@@ -1948,7 +1948,7 @@
         <v>79</v>
       </c>
       <c r="C34" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D34" s="2">
         <v>24.5</v>
@@ -1968,7 +1968,7 @@
         <v>81</v>
       </c>
       <c r="C35" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2">
         <v>28</v>
@@ -2028,7 +2028,7 @@
         <v>87</v>
       </c>
       <c r="C38" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" s="2">
         <v>19</v>
@@ -2091,7 +2091,7 @@
         <v>94</v>
       </c>
       <c r="C41" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D41" s="2">
         <v>18</v>
@@ -2111,7 +2111,7 @@
         <v>96</v>
       </c>
       <c r="C42" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2">
         <v>18</v>
@@ -2131,7 +2131,7 @@
         <v>98</v>
       </c>
       <c r="C43" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D43" s="2">
         <v>15</v>
@@ -2154,7 +2154,7 @@
         <v>101</v>
       </c>
       <c r="C44" s="2">
-        <v>236</v>
+        <v>281</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>103</v>
       </c>
       <c r="C45" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D45" s="2">
         <v>6</v>
@@ -2194,7 +2194,7 @@
         <v>105</v>
       </c>
       <c r="C46" s="2">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D46" s="2">
         <v>2.8</v>
@@ -2217,7 +2217,7 @@
         <v>108</v>
       </c>
       <c r="C47" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D47" s="2">
         <v>2.4</v>
@@ -2240,7 +2240,7 @@
         <v>111</v>
       </c>
       <c r="C48">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E48" s="4">
         <v>2900</v>
